--- a/Documentation/LRC ERD.xlsx
+++ b/Documentation/LRC ERD.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fmcgrath\Desktop\LRC\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\pype\cola\lrc-site\Documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -2751,7 +2751,7 @@
           <a:pPr algn="ctr"/>
           <a:r>
             <a:rPr lang="en-US" sz="1000" b="1" u="sng"/>
-            <a:t>EIEOL Head Word Keywords</a:t>
+            <a:t>EIEOL Glossed Text Gloss</a:t>
           </a:r>
         </a:p>
         <a:p>

--- a/Documentation/LRC ERD.xlsx
+++ b/Documentation/LRC ERD.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20295" windowHeight="9045"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="12630" windowHeight="7080"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1705,8 +1705,8 @@
     <xdr:to>
       <xdr:col>14</xdr:col>
       <xdr:colOff>33003</xdr:colOff>
-      <xdr:row>41</xdr:row>
-      <xdr:rowOff>177210</xdr:rowOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>165653</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1715,8 +1715,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6889011" y="6955466"/>
-          <a:ext cx="1672190" cy="941424"/>
+          <a:off x="6869588" y="7134601"/>
+          <a:ext cx="1666893" cy="1341269"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1771,7 +1771,31 @@
         </a:p>
         <a:p>
           <a:pPr algn="l"/>
-          <a:endParaRPr lang="en-US" sz="1000" baseline="0"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" baseline="0"/>
+            <a:t>Published</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" baseline="0"/>
+            <a:t>Menu Name</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" baseline="0"/>
+            <a:t>Menu Order</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" baseline="0"/>
+            <a:t>Expanded Title</a:t>
+          </a:r>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -1890,7 +1914,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>415222</xdr:colOff>
+      <xdr:colOff>414339</xdr:colOff>
       <xdr:row>36</xdr:row>
       <xdr:rowOff>177210</xdr:rowOff>
     </xdr:to>
@@ -1904,8 +1928,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipH="1" flipV="1">
-          <a:off x="7691880" y="6069419"/>
-          <a:ext cx="33226" cy="886047"/>
+          <a:off x="7670692" y="6228651"/>
+          <a:ext cx="32343" cy="905950"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -2007,16 +2031,15 @@
           <a:pPr algn="l"/>
           <a:r>
             <a:rPr lang="en-US" sz="1000"/>
+            <a:t>Glossed Text</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000"/>
             <a:t>Order</a:t>
           </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:r>
-            <a:rPr lang="en-US" sz="1000"/>
-            <a:t>Text</a:t>
-          </a:r>
-          <a:endParaRPr lang="en-US" sz="1000" baseline="0"/>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -2172,13 +2195,6 @@
             <a:t>Contextual Gloss</a:t>
           </a:r>
         </a:p>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:r>
-            <a:rPr lang="en-US" sz="1000" baseline="0"/>
-            <a:t>Display ID (lesson.row)??</a:t>
-          </a:r>
-        </a:p>
       </xdr:txBody>
     </xdr:sp>
     <xdr:clientData/>
@@ -2315,8 +2331,12 @@
         <a:p>
           <a:pPr algn="l"/>
           <a:r>
-            <a:rPr lang="en-US" sz="1000" baseline="0"/>
-            <a:t>Etyma ID</a:t>
+            <a:rPr lang="en-US" sz="1000" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Etyma ID - add later</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -2423,7 +2443,7 @@
           <a:pPr algn="ctr"/>
           <a:r>
             <a:rPr lang="en-US" sz="1000" b="1" u="sng"/>
-            <a:t>EIEOL Head Word Keywords</a:t>
+            <a:t>EIEOL Head Word Keyword</a:t>
           </a:r>
         </a:p>
         <a:p>
@@ -2555,15 +2575,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>15</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:colOff>55217</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>179457</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>17</xdr:col>
-      <xdr:colOff>453876</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>132907</xdr:rowOff>
+      <xdr:colOff>509093</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>119103</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2572,8 +2592,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="9137355" y="4707122"/>
-          <a:ext cx="1672190" cy="1262616"/>
+          <a:off x="9166087" y="5590761"/>
+          <a:ext cx="1668658" cy="1292472"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2637,7 +2657,7 @@
           <a:pPr algn="l"/>
           <a:r>
             <a:rPr lang="en-US" sz="1000"/>
-            <a:t>Text</a:t>
+            <a:t>Grammar Text</a:t>
           </a:r>
         </a:p>
         <a:p>
@@ -2653,16 +2673,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>608934</xdr:colOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>1543</xdr:colOff>
       <xdr:row>28</xdr:row>
-      <xdr:rowOff>66453</xdr:rowOff>
+      <xdr:rowOff>118783</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>28</xdr:row>
-      <xdr:rowOff>116294</xdr:rowOff>
+      <xdr:colOff>55217</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>52649</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -2673,9 +2693,9 @@
         </xdr:cNvCxnSpPr>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm flipV="1">
-          <a:off x="8527975" y="5338430"/>
-          <a:ext cx="609380" cy="49841"/>
+        <a:xfrm>
+          <a:off x="8505021" y="5530087"/>
+          <a:ext cx="661066" cy="706910"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -2817,6 +2837,370 @@
         <a:xfrm flipH="1">
           <a:off x="7678146" y="1661337"/>
           <a:ext cx="174550" cy="495743"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>69574</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>41412</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>523450</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>36827</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="42" name="Rectangle 41"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9180444" y="4293151"/>
+          <a:ext cx="1668658" cy="768459"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" b="1" u="sng"/>
+            <a:t>EIEOL Language</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000"/>
+            <a:t>ID</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000"/>
+            <a:t>Language</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1000" baseline="0"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>1543</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>82826</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>55217</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>118783</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="43" name="Straight Arrow Connector 42"/>
+        <xdr:cNvCxnSpPr>
+          <a:endCxn id="28" idx="3"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="8505021" y="4721087"/>
+          <a:ext cx="661066" cy="809000"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>262282</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>82826</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>108767</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>78242</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="46" name="Rectangle 45"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9373152" y="276087"/>
+          <a:ext cx="1668658" cy="768459"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" b="1" u="sng"/>
+            <a:t>EIEOL Part Of Speech</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000"/>
+            <a:t>ID</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000"/>
+            <a:t>Language</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1000" baseline="0"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>303695</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>96631</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>150180</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>92046</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="49" name="Rectangle 48"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9414565" y="1449457"/>
+          <a:ext cx="1668658" cy="768459"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" b="1" u="sng"/>
+            <a:t>EIEOL Analysis</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000"/>
+            <a:t>ID</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" baseline="0"/>
+            <a:t>Analysis</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>160593</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>80534</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>262282</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>97022</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="50" name="Straight Arrow Connector 49"/>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="46" idx="1"/>
+          <a:endCxn id="37" idx="3"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="8664071" y="660317"/>
+          <a:ext cx="709081" cy="209748"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>160593</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>97022</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>303695</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>94339</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="56" name="Straight Arrow Connector 55"/>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="49" idx="1"/>
+          <a:endCxn id="37" idx="3"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1" flipV="1">
+          <a:off x="8664071" y="870065"/>
+          <a:ext cx="750494" cy="963622"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>

--- a/Documentation/LRC ERD.xlsx
+++ b/Documentation/LRC ERD.xlsx
@@ -9,10 +9,10 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="12630" windowHeight="7080"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="12630" windowHeight="5145"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
   </sheets>
   <calcPr calcId="152511"/>
   <extLst>
@@ -95,8 +95,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1905665" y="2941451"/>
-          <a:ext cx="1549916" cy="1067909"/>
+          <a:off x="1906994" y="2974678"/>
+          <a:ext cx="1550802" cy="1081199"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -193,8 +193,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="0" y="3016325"/>
-          <a:ext cx="1374921" cy="904432"/>
+          <a:off x="0" y="3051767"/>
+          <a:ext cx="1375807" cy="913292"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -272,7 +272,7 @@
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="5" name="Straight Arrow Connector 4"/>
+        <xdr:cNvPr id="4" name="Straight Arrow Connector 3"/>
         <xdr:cNvCxnSpPr>
           <a:stCxn id="2" idx="1"/>
           <a:endCxn id="3" idx="3"/>
@@ -280,8 +280,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipH="1" flipV="1">
-          <a:off x="1374921" y="3468541"/>
-          <a:ext cx="530744" cy="6865"/>
+          <a:off x="1375807" y="3508413"/>
+          <a:ext cx="531187" cy="6865"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -322,13 +322,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="7" name="Rectangle 6"/>
+        <xdr:cNvPr id="5" name="Rectangle 4"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
           <a:off x="52278" y="46295"/>
-          <a:ext cx="1398847" cy="1083414"/>
+          <a:ext cx="1399733" cy="1096705"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -405,6 +405,419 @@
       <xdr:colOff>509477</xdr:colOff>
       <xdr:row>5</xdr:row>
       <xdr:rowOff>166133</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="6" name="Rectangle 5"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1884401" y="36770"/>
+          <a:ext cx="1673076" cy="1081863"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" b="1" u="sng"/>
+            <a:t>Pokorny Semantic Field</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1000"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000"/>
+            <a:t>ID</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000"/>
+            <a:t>Text</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000"/>
+            <a:t>Number</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000"/>
+            <a:t>Abbr</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000"/>
+            <a:t>Semantic</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" baseline="0"/>
+            <a:t> </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000"/>
+            <a:t>Category</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" baseline="0"/>
+            <a:t> ID</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>232811</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>7309</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>55601</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>23147</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="7" name="Straight Arrow Connector 6"/>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="5" idx="3"/>
+          <a:endCxn id="6" idx="1"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="1452011" y="578809"/>
+          <a:ext cx="432390" cy="15838"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>461453</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>103457</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>377052</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>102567</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="8" name="Rectangle 7"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1680653" y="1436957"/>
+          <a:ext cx="1744399" cy="761110"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" b="1" u="sng"/>
+            <a:t>Pokorny Semantic Etyma</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1000"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000"/>
+            <a:t>ID</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000"/>
+            <a:t>Semantic Field ID</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" baseline="0"/>
+            <a:t>Etyma ID</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>115558</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>166133</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>282540</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>103457</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="9" name="Straight Arrow Connector 8"/>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="6" idx="2"/>
+          <a:endCxn id="8" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="2553958" y="1118633"/>
+          <a:ext cx="166982" cy="318324"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>115558</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>102567</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>243996</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>117178</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="10" name="Straight Arrow Connector 9"/>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="2" idx="0"/>
+          <a:endCxn id="8" idx="2"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1" flipV="1">
+          <a:off x="2553958" y="2198067"/>
+          <a:ext cx="128438" cy="776611"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>587006</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>11076</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>509476</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>143983</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="11" name="Rectangle 10"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4244606" y="8012076"/>
+          <a:ext cx="1141670" cy="894907"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" b="1" u="sng"/>
+            <a:t>Pokorny Language Family</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1000"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000"/>
+            <a:t>ID</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000"/>
+            <a:t>Name</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" baseline="0"/>
+            <a:t>Order</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>540047</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>177209</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>564857</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>143985</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -413,8 +826,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1883072" y="36770"/>
-          <a:ext cx="1672190" cy="1070787"/>
+          <a:off x="4197647" y="6463709"/>
+          <a:ext cx="1244010" cy="1109776"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -443,7 +856,7 @@
           <a:pPr algn="ctr"/>
           <a:r>
             <a:rPr lang="en-US" sz="1000" b="1" u="sng"/>
-            <a:t>Pokorny Semantic Field</a:t>
+            <a:t>Pokorny Language Sub Family</a:t>
           </a:r>
           <a:endParaRPr lang="en-US" sz="1000"/>
         </a:p>
@@ -458,40 +871,21 @@
           <a:pPr algn="l"/>
           <a:r>
             <a:rPr lang="en-US" sz="1000"/>
-            <a:t>Text</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:r>
-            <a:rPr lang="en-US" sz="1000"/>
-            <a:t>Number</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:r>
-            <a:rPr lang="en-US" sz="1000"/>
-            <a:t>Abbr</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:r>
-            <a:rPr lang="en-US" sz="1000"/>
-            <a:t>Semantic</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1000" baseline="0"/>
-            <a:t> </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1000"/>
-            <a:t>Category</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1000" baseline="0"/>
-            <a:t> ID</a:t>
+            <a:t>Name</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" baseline="0"/>
+            <a:t>Order</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" baseline="0"/>
+            <a:t>Family ID</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -500,29 +894,29 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>232811</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>7309</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>55601</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>23147</xdr:rowOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>548241</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>143985</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>552452</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>11076</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="14" name="Straight Arrow Connector 13"/>
+        <xdr:cNvPr id="13" name="Straight Arrow Connector 12"/>
         <xdr:cNvCxnSpPr>
-          <a:stCxn id="7" idx="3"/>
-          <a:endCxn id="12" idx="1"/>
+          <a:stCxn id="11" idx="0"/>
+          <a:endCxn id="12" idx="2"/>
         </xdr:cNvCxnSpPr>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipV="1">
-          <a:off x="1451125" y="572164"/>
-          <a:ext cx="431947" cy="15838"/>
+          <a:off x="4815441" y="7573485"/>
+          <a:ext cx="4211" cy="438591"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -551,25 +945,25 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>19714</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>144870</xdr:rowOff>
+      <xdr:colOff>31233</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>11075</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>542704</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>143981</xdr:rowOff>
+      <xdr:colOff>487325</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>77528</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="40" name="Rectangle 39"/>
+        <xdr:cNvPr id="14" name="Rectangle 13"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1847185" y="1651149"/>
-          <a:ext cx="1741304" cy="752251"/>
+          <a:off x="1860033" y="5916575"/>
+          <a:ext cx="1675292" cy="1399953"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -598,29 +992,61 @@
           <a:pPr algn="ctr"/>
           <a:r>
             <a:rPr lang="en-US" sz="1000" b="1" u="sng"/>
-            <a:t>Pokorny Semantic Etyma</a:t>
-          </a:r>
-          <a:endParaRPr lang="en-US" sz="1000"/>
-        </a:p>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:r>
-            <a:rPr lang="en-US" sz="1000"/>
+            <a:t>Pokorny</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" b="1" u="sng" baseline="0"/>
+            <a:t> Reflex</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1000" baseline="0"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" baseline="0"/>
             <a:t>ID</a:t>
           </a:r>
         </a:p>
         <a:p>
           <a:pPr algn="l"/>
           <a:r>
-            <a:rPr lang="en-US" sz="1000"/>
-            <a:t>Semantic Field ID</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:r>
-            <a:rPr lang="en-US" sz="1000" baseline="0"/>
-            <a:t>Etyma ID</a:t>
+            <a:rPr lang="en-US" sz="1000" baseline="0"/>
+            <a:t>Language ID</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" baseline="0"/>
+            <a:t>Source ID</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" baseline="0"/>
+            <a:t>Part of Speech ID</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" baseline="0"/>
+            <a:t>reflex</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" baseline="0"/>
+            <a:t>html language code</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" baseline="0"/>
+            <a:t>gloss</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -629,29 +1055,29 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>281209</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>166133</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>282539</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>144870</xdr:rowOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>552452</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>33227</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>570392</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>177209</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="45" name="Straight Arrow Connector 44"/>
+        <xdr:cNvPr id="15" name="Straight Arrow Connector 14"/>
         <xdr:cNvCxnSpPr>
-          <a:stCxn id="12" idx="2"/>
-          <a:endCxn id="40" idx="0"/>
+          <a:stCxn id="12" idx="0"/>
+          <a:endCxn id="21" idx="2"/>
         </xdr:cNvCxnSpPr>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm flipH="1">
-          <a:off x="2717837" y="1107557"/>
-          <a:ext cx="1330" cy="543592"/>
+        <a:xfrm flipV="1">
+          <a:off x="4819652" y="5938727"/>
+          <a:ext cx="17940" cy="524982"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -679,76 +1105,26 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>243995</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>143981</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>281209</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>117178</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="47" name="Straight Arrow Connector 46"/>
-        <xdr:cNvCxnSpPr>
-          <a:stCxn id="2" idx="0"/>
-          <a:endCxn id="40" idx="2"/>
-        </xdr:cNvCxnSpPr>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm flipV="1">
-          <a:off x="2680623" y="2403400"/>
-          <a:ext cx="37214" cy="538051"/>
-        </a:xfrm>
-        <a:prstGeom prst="straightConnector1">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln>
-          <a:tailEnd type="triangle"/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>143983</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>44303</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
       <xdr:colOff>587006</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>11076</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>509476</xdr:colOff>
-      <xdr:row>46</xdr:row>
-      <xdr:rowOff>143983</xdr:rowOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>44302</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="51" name="Rectangle 50"/>
+        <xdr:cNvPr id="16" name="Rectangle 15"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4241948" y="7919041"/>
-          <a:ext cx="1140784" cy="886047"/>
+          <a:off x="143983" y="7283303"/>
+          <a:ext cx="1052623" cy="952499"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -777,29 +1153,33 @@
           <a:pPr algn="ctr"/>
           <a:r>
             <a:rPr lang="en-US" sz="1000" b="1" u="sng"/>
-            <a:t>Pokorny Language Family</a:t>
-          </a:r>
-          <a:endParaRPr lang="en-US" sz="1000"/>
-        </a:p>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:r>
-            <a:rPr lang="en-US" sz="1000"/>
+            <a:t>Pokorny</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" b="1" u="sng" baseline="0"/>
+            <a:t> Part Of Speech</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1000" baseline="0"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" baseline="0"/>
             <a:t>ID</a:t>
           </a:r>
         </a:p>
         <a:p>
           <a:pPr algn="l"/>
           <a:r>
-            <a:rPr lang="en-US" sz="1000"/>
-            <a:t>Name</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:r>
-            <a:rPr lang="en-US" sz="1000" baseline="0"/>
-            <a:t>Order</a:t>
+            <a:rPr lang="en-US" sz="1000" baseline="0"/>
+            <a:t>Code</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" baseline="0"/>
+            <a:t>Display</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -808,26 +1188,26 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>540047</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>177209</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>564857</xdr:colOff>
-      <xdr:row>39</xdr:row>
-      <xdr:rowOff>143985</xdr:rowOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>44302</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>52720</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>55378</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>88604</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="52" name="Rectangle 51"/>
+        <xdr:cNvPr id="17" name="Rectangle 16"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4194989" y="6390610"/>
-          <a:ext cx="1243124" cy="1096485"/>
+          <a:off x="44302" y="5767720"/>
+          <a:ext cx="1230276" cy="797884"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -856,36 +1236,33 @@
           <a:pPr algn="ctr"/>
           <a:r>
             <a:rPr lang="en-US" sz="1000" b="1" u="sng"/>
-            <a:t>Pokorny Language Sub Family</a:t>
-          </a:r>
-          <a:endParaRPr lang="en-US" sz="1000"/>
-        </a:p>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:r>
-            <a:rPr lang="en-US" sz="1000"/>
+            <a:t>Pokorny</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" b="1" u="sng" baseline="0"/>
+            <a:t> Source</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1000" baseline="0"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" baseline="0"/>
             <a:t>ID</a:t>
           </a:r>
         </a:p>
         <a:p>
           <a:pPr algn="l"/>
           <a:r>
-            <a:rPr lang="en-US" sz="1000"/>
-            <a:t>Name</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:r>
-            <a:rPr lang="en-US" sz="1000" baseline="0"/>
-            <a:t>Order</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:r>
-            <a:rPr lang="en-US" sz="1000" baseline="0"/>
-            <a:t>Family ID</a:t>
+            <a:rPr lang="en-US" sz="1000" baseline="0"/>
+            <a:t>Code</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" baseline="0"/>
+            <a:t>Display</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -894,29 +1271,29 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>548241</xdr:colOff>
-      <xdr:row>39</xdr:row>
-      <xdr:rowOff>143985</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>552452</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>11076</xdr:rowOff>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>55378</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>70663</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>31233</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>138444</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="54" name="Straight Arrow Connector 53"/>
+        <xdr:cNvPr id="18" name="Straight Arrow Connector 17"/>
         <xdr:cNvCxnSpPr>
-          <a:stCxn id="51" idx="0"/>
-          <a:endCxn id="52" idx="2"/>
+          <a:stCxn id="17" idx="3"/>
+          <a:endCxn id="14" idx="1"/>
         </xdr:cNvCxnSpPr>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm flipV="1">
-          <a:off x="4812340" y="7487095"/>
-          <a:ext cx="4211" cy="431946"/>
+        <a:xfrm>
+          <a:off x="1274578" y="6166663"/>
+          <a:ext cx="585455" cy="448781"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -944,26 +1321,126 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>587006</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>138444</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>31233</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>138446</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="19" name="Straight Arrow Connector 18"/>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="16" idx="3"/>
+          <a:endCxn id="14" idx="1"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="1196606" y="6615444"/>
+          <a:ext cx="663427" cy="1143002"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>242333</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>55377</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>243995</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>22152</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="20" name="Straight Arrow Connector 19"/>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="2" idx="2"/>
+          <a:endCxn id="23" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="2680733" y="4055877"/>
+          <a:ext cx="1662" cy="538275"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>498400</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>121834</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>33226</xdr:colOff>
       <xdr:row>31</xdr:row>
-      <xdr:rowOff>11075</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>487325</xdr:colOff>
-      <xdr:row>38</xdr:row>
-      <xdr:rowOff>77528</xdr:rowOff>
+      <xdr:rowOff>33227</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="55" name="Rectangle 54"/>
+        <xdr:cNvPr id="21" name="Rectangle 20"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1858704" y="5847906"/>
-          <a:ext cx="1674406" cy="1384448"/>
+          <a:off x="4156000" y="4884334"/>
+          <a:ext cx="1363626" cy="1054393"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -992,61 +1469,43 @@
           <a:pPr algn="ctr"/>
           <a:r>
             <a:rPr lang="en-US" sz="1000" b="1" u="sng"/>
-            <a:t>Pokorny</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1000" b="1" u="sng" baseline="0"/>
-            <a:t> Reflex</a:t>
-          </a:r>
-          <a:endParaRPr lang="en-US" sz="1000" baseline="0"/>
-        </a:p>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:r>
-            <a:rPr lang="en-US" sz="1000" baseline="0"/>
+            <a:t>Pokorny Language </a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1000"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000"/>
             <a:t>ID</a:t>
           </a:r>
         </a:p>
         <a:p>
           <a:pPr algn="l"/>
           <a:r>
-            <a:rPr lang="en-US" sz="1000" baseline="0"/>
-            <a:t>Language ID</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:r>
-            <a:rPr lang="en-US" sz="1000" baseline="0"/>
-            <a:t>Source ID</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:r>
-            <a:rPr lang="en-US" sz="1000" baseline="0"/>
-            <a:t>Part of Speech ID</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:r>
-            <a:rPr lang="en-US" sz="1000" baseline="0"/>
-            <a:t>reflex</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:r>
-            <a:rPr lang="en-US" sz="1000" baseline="0"/>
-            <a:t>html language code</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:r>
-            <a:rPr lang="en-US" sz="1000" baseline="0"/>
-            <a:t>gloss</a:t>
+            <a:rPr lang="en-US" sz="1000"/>
+            <a:t>Name</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" baseline="0"/>
+            <a:t>Abbr</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" baseline="0"/>
+            <a:t>AKA</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" baseline="0"/>
+            <a:t>Sub Family ID</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -1055,29 +1514,29 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>552452</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>33227</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>570392</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>177209</xdr:rowOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>487325</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>77530</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>498400</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>138444</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="61" name="Straight Arrow Connector 60"/>
+        <xdr:cNvPr id="22" name="Straight Arrow Connector 21"/>
         <xdr:cNvCxnSpPr>
-          <a:stCxn id="52" idx="0"/>
-          <a:endCxn id="87" idx="2"/>
+          <a:stCxn id="21" idx="1"/>
+          <a:endCxn id="14" idx="3"/>
         </xdr:cNvCxnSpPr>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm flipV="1">
-          <a:off x="4816551" y="5870058"/>
-          <a:ext cx="17940" cy="520552"/>
+        <a:xfrm flipH="1">
+          <a:off x="3535325" y="5411530"/>
+          <a:ext cx="620675" cy="1203914"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -1105,26 +1564,26 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>143983</xdr:colOff>
-      <xdr:row>38</xdr:row>
-      <xdr:rowOff>44303</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>587006</xdr:colOff>
-      <xdr:row>43</xdr:row>
-      <xdr:rowOff>44302</xdr:rowOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>152399</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>22152</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>332266</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>155059</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="62" name="Rectangle 61"/>
+        <xdr:cNvPr id="23" name="Rectangle 22"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="143983" y="7199129"/>
-          <a:ext cx="1052180" cy="941423"/>
+          <a:off x="1981199" y="4594152"/>
+          <a:ext cx="1399067" cy="894907"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1157,465 +1616,6 @@
           </a:r>
           <a:r>
             <a:rPr lang="en-US" sz="1000" b="1" u="sng" baseline="0"/>
-            <a:t> Part Of Speech</a:t>
-          </a:r>
-          <a:endParaRPr lang="en-US" sz="1000" baseline="0"/>
-        </a:p>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:r>
-            <a:rPr lang="en-US" sz="1000" baseline="0"/>
-            <a:t>ID</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:r>
-            <a:rPr lang="en-US" sz="1000" baseline="0"/>
-            <a:t>Code</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:r>
-            <a:rPr lang="en-US" sz="1000" baseline="0"/>
-            <a:t>Display</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>44302</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>52720</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>55378</xdr:colOff>
-      <xdr:row>34</xdr:row>
-      <xdr:rowOff>88604</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="63" name="Rectangle 62"/>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="44302" y="5701267"/>
-          <a:ext cx="1229390" cy="789023"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="50000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="en-US" sz="1000" b="1" u="sng"/>
-            <a:t>Pokorny</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1000" b="1" u="sng" baseline="0"/>
-            <a:t> Source</a:t>
-          </a:r>
-          <a:endParaRPr lang="en-US" sz="1000" baseline="0"/>
-        </a:p>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:r>
-            <a:rPr lang="en-US" sz="1000" baseline="0"/>
-            <a:t>ID</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:r>
-            <a:rPr lang="en-US" sz="1000" baseline="0"/>
-            <a:t>Code</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:r>
-            <a:rPr lang="en-US" sz="1000" baseline="0"/>
-            <a:t>Display</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>55378</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>70663</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>31233</xdr:colOff>
-      <xdr:row>34</xdr:row>
-      <xdr:rowOff>138444</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="65" name="Straight Arrow Connector 64"/>
-        <xdr:cNvCxnSpPr>
-          <a:stCxn id="63" idx="3"/>
-          <a:endCxn id="55" idx="1"/>
-        </xdr:cNvCxnSpPr>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1273692" y="6095779"/>
-          <a:ext cx="585012" cy="444351"/>
-        </a:xfrm>
-        <a:prstGeom prst="straightConnector1">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln>
-          <a:tailEnd type="triangle"/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>587006</xdr:colOff>
-      <xdr:row>34</xdr:row>
-      <xdr:rowOff>138444</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>31233</xdr:colOff>
-      <xdr:row>40</xdr:row>
-      <xdr:rowOff>138446</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="67" name="Straight Arrow Connector 66"/>
-        <xdr:cNvCxnSpPr>
-          <a:stCxn id="62" idx="3"/>
-          <a:endCxn id="55" idx="1"/>
-        </xdr:cNvCxnSpPr>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm flipV="1">
-          <a:off x="1196163" y="6540130"/>
-          <a:ext cx="662541" cy="1129711"/>
-        </a:xfrm>
-        <a:prstGeom prst="straightConnector1">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln>
-          <a:tailEnd type="triangle"/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>242333</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>55377</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>243995</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>22152</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="74" name="Straight Arrow Connector 73"/>
-        <xdr:cNvCxnSpPr>
-          <a:stCxn id="2" idx="2"/>
-          <a:endCxn id="250" idx="0"/>
-        </xdr:cNvCxnSpPr>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm flipH="1">
-          <a:off x="2678961" y="4009360"/>
-          <a:ext cx="1662" cy="531629"/>
-        </a:xfrm>
-        <a:prstGeom prst="straightConnector1">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln>
-          <a:tailEnd type="triangle"/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>498400</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>121834</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>33226</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>33227</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="87" name="Rectangle 86"/>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="4153342" y="4828956"/>
-          <a:ext cx="1362297" cy="1041102"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="50000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="en-US" sz="1000" b="1" u="sng"/>
-            <a:t>Pokorny Language </a:t>
-          </a:r>
-          <a:endParaRPr lang="en-US" sz="1000"/>
-        </a:p>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:r>
-            <a:rPr lang="en-US" sz="1000"/>
-            <a:t>ID</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:r>
-            <a:rPr lang="en-US" sz="1000"/>
-            <a:t>Name</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:r>
-            <a:rPr lang="en-US" sz="1000" baseline="0"/>
-            <a:t>Abbr</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:r>
-            <a:rPr lang="en-US" sz="1000" baseline="0"/>
-            <a:t>AKA</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:r>
-            <a:rPr lang="en-US" sz="1000" baseline="0"/>
-            <a:t>Sub Family ID</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>487325</xdr:colOff>
-      <xdr:row>28</xdr:row>
-      <xdr:rowOff>77530</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>498400</xdr:colOff>
-      <xdr:row>34</xdr:row>
-      <xdr:rowOff>138444</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="91" name="Straight Arrow Connector 90"/>
-        <xdr:cNvCxnSpPr>
-          <a:stCxn id="87" idx="1"/>
-          <a:endCxn id="55" idx="3"/>
-        </xdr:cNvCxnSpPr>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm flipH="1">
-          <a:off x="3533110" y="5349507"/>
-          <a:ext cx="620232" cy="1190623"/>
-        </a:xfrm>
-        <a:prstGeom prst="straightConnector1">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln>
-          <a:tailEnd type="triangle"/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>152399</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>22152</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>332266</xdr:colOff>
-      <xdr:row>28</xdr:row>
-      <xdr:rowOff>155059</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="250" name="Rectangle 249"/>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1979870" y="4540989"/>
-          <a:ext cx="1398181" cy="886047"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="50000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="en-US" sz="1000" b="1" u="sng"/>
-            <a:t>Pokorny</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1000" b="1" u="sng" baseline="0"/>
             <a:t>  Etyma Reflex</a:t>
           </a:r>
           <a:endParaRPr lang="en-US" sz="1000" baseline="0"/>
@@ -1660,16 +1660,16 @@
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="284" name="Straight Arrow Connector 283"/>
+        <xdr:cNvPr id="24" name="Straight Arrow Connector 23"/>
         <xdr:cNvCxnSpPr>
-          <a:stCxn id="55" idx="0"/>
-          <a:endCxn id="250" idx="2"/>
+          <a:stCxn id="14" idx="0"/>
+          <a:endCxn id="23" idx="2"/>
         </xdr:cNvCxnSpPr>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipH="1" flipV="1">
-          <a:off x="2678961" y="5427036"/>
-          <a:ext cx="16946" cy="420870"/>
+          <a:off x="2680733" y="5489059"/>
+          <a:ext cx="16946" cy="427516"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -1698,15 +1698,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>11</xdr:col>
-      <xdr:colOff>188284</xdr:colOff>
-      <xdr:row>36</xdr:row>
-      <xdr:rowOff>177210</xdr:rowOff>
+      <xdr:colOff>229697</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>80579</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>14</xdr:col>
-      <xdr:colOff>33003</xdr:colOff>
-      <xdr:row>43</xdr:row>
-      <xdr:rowOff>165653</xdr:rowOff>
+      <xdr:colOff>74416</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>69022</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1715,7 +1715,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6869588" y="7134601"/>
+          <a:off x="6911001" y="8004275"/>
           <a:ext cx="1666893" cy="1341269"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1804,15 +1804,176 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>11</xdr:col>
-      <xdr:colOff>155058</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>1</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>608934</xdr:colOff>
+      <xdr:colOff>196471</xdr:colOff>
       <xdr:row>32</xdr:row>
-      <xdr:rowOff>44303</xdr:rowOff>
+      <xdr:rowOff>27609</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>42956</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>71911</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="26" name="Rectangle 25"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6877775" y="6211957"/>
+          <a:ext cx="1668659" cy="1397128"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" b="1" u="sng"/>
+            <a:t>EIEOL Lesson</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000"/>
+            <a:t>ID</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000"/>
+            <a:t>Series ID</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000"/>
+            <a:t>Title</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000"/>
+            <a:t>Order (0 is intro)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000"/>
+            <a:t>Language ID</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000"/>
+            <a:t>Intro Text</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" baseline="0"/>
+            <a:t>Lesson Translation</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1000"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1000" baseline="0"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>423409</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>71911</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>455752</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>80579</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="27" name="Straight Arrow Connector 26"/>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="25" idx="0"/>
+          <a:endCxn id="26" idx="2"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1" flipV="1">
+          <a:off x="7712105" y="7609085"/>
+          <a:ext cx="32343" cy="395190"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>168934</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>149672</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>15419</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>190532</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1821,8 +1982,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6855785" y="4707123"/>
-          <a:ext cx="1672190" cy="1362296"/>
+          <a:off x="6850238" y="4787933"/>
+          <a:ext cx="1668659" cy="1007164"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1851,8 +2012,13 @@
           <a:pPr algn="ctr"/>
           <a:r>
             <a:rPr lang="en-US" sz="1000" b="1" u="sng"/>
-            <a:t>EIEOL Lesson</a:t>
-          </a:r>
+            <a:t>EIEOL Glossed</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" b="1" u="sng" baseline="0"/>
+            <a:t> Text</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1000" b="1" u="sng"/>
         </a:p>
         <a:p>
           <a:pPr algn="l"/>
@@ -1865,41 +2031,22 @@
           <a:pPr algn="l"/>
           <a:r>
             <a:rPr lang="en-US" sz="1000"/>
-            <a:t>Series ID</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:r>
-            <a:rPr lang="en-US" sz="1000"/>
-            <a:t>Title</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:r>
-            <a:rPr lang="en-US" sz="1000"/>
-            <a:t>Order (0 is intro)</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:r>
-            <a:rPr lang="en-US" sz="1000"/>
-            <a:t>Intro Text</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:r>
-            <a:rPr lang="en-US" sz="1000" baseline="0"/>
-            <a:t>Lesson Translation</a:t>
-          </a:r>
-          <a:endParaRPr lang="en-US" sz="1000"/>
-        </a:p>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr lang="en-US" sz="1000" baseline="0"/>
+            <a:t>Lesson ID</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000"/>
+            <a:t>Glossed Text</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000"/>
+            <a:t>Order</a:t>
+          </a:r>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -1908,28 +2055,28 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>381996</xdr:colOff>
+      <xdr:colOff>395872</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>190532</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>423409</xdr:colOff>
       <xdr:row>32</xdr:row>
-      <xdr:rowOff>44303</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>414339</xdr:colOff>
-      <xdr:row>36</xdr:row>
-      <xdr:rowOff>177210</xdr:rowOff>
+      <xdr:rowOff>27609</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="6" name="Straight Arrow Connector 5"/>
+        <xdr:cNvPr id="29" name="Straight Arrow Connector 28"/>
         <xdr:cNvCxnSpPr>
-          <a:stCxn id="25" idx="0"/>
+          <a:stCxn id="26" idx="0"/>
           <a:endCxn id="28" idx="2"/>
         </xdr:cNvCxnSpPr>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipH="1" flipV="1">
-          <a:off x="7670692" y="6228651"/>
-          <a:ext cx="32343" cy="905950"/>
+          <a:off x="7684568" y="5795097"/>
+          <a:ext cx="27537" cy="416860"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -1958,25 +2105,25 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>11</xdr:col>
-      <xdr:colOff>141324</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>163476</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>595200</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>11075</xdr:rowOff>
+      <xdr:colOff>219244</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>38984</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>63963</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="33" name="Rectangle 32"/>
+        <xdr:cNvPr id="30" name="Rectangle 29"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6842051" y="3364319"/>
-          <a:ext cx="1672190" cy="977308"/>
+          <a:off x="6900548" y="232245"/>
+          <a:ext cx="1666893" cy="1313842"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2005,41 +2152,126 @@
           <a:pPr algn="ctr"/>
           <a:r>
             <a:rPr lang="en-US" sz="1000" b="1" u="sng"/>
-            <a:t>EIEOL Glossed</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1000" b="1" u="sng" baseline="0"/>
-            <a:t> Text</a:t>
-          </a:r>
-          <a:endParaRPr lang="en-US" sz="1000" b="1" u="sng"/>
-        </a:p>
-        <a:p>
-          <a:pPr algn="l"/>
+            <a:t>EIEOL Element</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:tabLst/>
+            <a:defRPr/>
+          </a:pPr>
           <a:r>
             <a:rPr lang="en-US" sz="1000"/>
             <a:t>ID</a:t>
           </a:r>
         </a:p>
         <a:p>
-          <a:pPr algn="l"/>
-          <a:r>
-            <a:rPr lang="en-US" sz="1000"/>
-            <a:t>Lesson ID</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:r>
-            <a:rPr lang="en-US" sz="1000"/>
-            <a:t>Glossed Text</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:r>
-            <a:rPr lang="en-US" sz="1000"/>
-            <a:t>Order</a:t>
-          </a:r>
+          <a:pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:tabLst/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" b="0" u="none" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Gloss Id</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1000" b="0" u="none"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" b="0" u="none" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Part of speech</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" b="0" i="0" u="none" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Analysis</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1000" b="0" u="none" baseline="0">
+            <a:solidFill>
+              <a:schemeClr val="bg1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Head Word ID</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1100" baseline="0">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>order</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1000" baseline="0"/>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -2049,27 +2281,27 @@
     <xdr:from>
       <xdr:col>12</xdr:col>
       <xdr:colOff>368262</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>11075</xdr:rowOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>105458</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>381996</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>1</xdr:rowOff>
+      <xdr:colOff>395872</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>149672</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="11" name="Straight Arrow Connector 10"/>
+        <xdr:cNvPr id="31" name="Straight Arrow Connector 30"/>
         <xdr:cNvCxnSpPr>
           <a:stCxn id="28" idx="0"/>
-          <a:endCxn id="33" idx="2"/>
+          <a:endCxn id="39" idx="2"/>
         </xdr:cNvCxnSpPr>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipH="1" flipV="1">
-          <a:off x="7678146" y="4341627"/>
-          <a:ext cx="13734" cy="365496"/>
+          <a:off x="7656958" y="4357197"/>
+          <a:ext cx="27610" cy="430736"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -2097,26 +2329,26 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>315874</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>38985</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>160593</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>155058</xdr:rowOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>381064</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>96631</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>227549</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>193191</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="37" name="Rectangle 36"/>
+        <xdr:cNvPr id="32" name="Rectangle 31"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7016601" y="38985"/>
-          <a:ext cx="1672190" cy="1622352"/>
+          <a:off x="4648264" y="287131"/>
+          <a:ext cx="1675285" cy="1239560"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2145,160 +2377,6 @@
           <a:pPr algn="ctr"/>
           <a:r>
             <a:rPr lang="en-US" sz="1000" b="1" u="sng"/>
-            <a:t>EIEOL Gloss</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:r>
-            <a:rPr lang="en-US" sz="1000"/>
-            <a:t>ID</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:r>
-            <a:rPr lang="en-US" sz="1000" b="1" u="sng"/>
-            <a:t>Surface</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1000" b="1" u="sng" baseline="0"/>
-            <a:t> Form</a:t>
-          </a:r>
-          <a:endParaRPr lang="en-US" sz="1000" b="1" u="sng"/>
-        </a:p>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:r>
-            <a:rPr lang="en-US" sz="1000" b="1" u="sng" baseline="0"/>
-            <a:t>Part of speech</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:r>
-            <a:rPr lang="en-US" sz="1000" b="1" i="0" u="sng" baseline="0"/>
-            <a:t>Analysis</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:r>
-            <a:rPr lang="en-US" sz="1000" baseline="0"/>
-            <a:t>Head Word ID</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:r>
-            <a:rPr lang="en-US" sz="1000" baseline="0"/>
-            <a:t>Contextual Gloss</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>368262</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>188284</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>368262</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>163476</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="16" name="Straight Arrow Connector 15"/>
-        <xdr:cNvCxnSpPr>
-          <a:stCxn id="33" idx="0"/>
-          <a:endCxn id="59" idx="2"/>
-        </xdr:cNvCxnSpPr>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm flipV="1">
-          <a:off x="7678146" y="3012557"/>
-          <a:ext cx="0" cy="351762"/>
-        </a:xfrm>
-        <a:prstGeom prst="straightConnector1">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln>
-          <a:tailEnd type="triangle"/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>22150</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>166135</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>476026</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>13734</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="48" name="Rectangle 47"/>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="4286249" y="1672414"/>
-          <a:ext cx="1672190" cy="977308"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="50000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="en-US" sz="1000" b="1" u="sng"/>
             <a:t>EIEOL Head Word</a:t>
           </a:r>
         </a:p>
@@ -2327,6 +2405,40 @@
             <a:rPr lang="en-US" sz="1000" b="1" u="sng" baseline="0"/>
             <a:t>Definition</a:t>
           </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:tabLst/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Language ID</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1000">
+            <a:effectLst/>
+          </a:endParaRPr>
         </a:p>
         <a:p>
           <a:pPr algn="l"/>
@@ -2345,29 +2457,29 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>476026</xdr:colOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>227549</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>97021</xdr:rowOff>
+      <xdr:rowOff>116123</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>11</xdr:col>
-      <xdr:colOff>315874</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>89934</xdr:rowOff>
+      <xdr:colOff>219244</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>144912</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="30" name="Straight Arrow Connector 29"/>
+        <xdr:cNvPr id="33" name="Straight Arrow Connector 32"/>
         <xdr:cNvCxnSpPr>
-          <a:stCxn id="48" idx="3"/>
-          <a:endCxn id="37" idx="1"/>
+          <a:stCxn id="32" idx="3"/>
+          <a:endCxn id="30" idx="1"/>
         </xdr:cNvCxnSpPr>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipV="1">
-          <a:off x="5958439" y="850161"/>
-          <a:ext cx="1058162" cy="1310907"/>
+          <a:off x="6301462" y="889166"/>
+          <a:ext cx="599086" cy="28789"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -2395,26 +2507,26 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>22151</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>11076</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>476027</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>55377</xdr:rowOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>505303</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>176728</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>351789</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>55216</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="53" name="Rectangle 52"/>
+        <xdr:cNvPr id="34" name="Rectangle 33"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4286250" y="387646"/>
-          <a:ext cx="1672190" cy="797440"/>
+          <a:off x="3553303" y="2081728"/>
+          <a:ext cx="1675286" cy="1021488"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2466,7 +2578,13 @@
             <a:rPr lang="en-US" sz="1000"/>
             <a:t>Keyword</a:t>
           </a:r>
-          <a:endParaRPr lang="en-US" sz="1000" baseline="0"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" baseline="0"/>
+            <a:t>Language ID</a:t>
+          </a:r>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -2474,29 +2592,29 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>249088</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>55377</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>249089</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>166135</xdr:rowOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>124851</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>193191</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>611</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>176728</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
         <xdr:cNvPr id="35" name="Straight Arrow Connector 34"/>
         <xdr:cNvCxnSpPr>
-          <a:stCxn id="48" idx="0"/>
-          <a:endCxn id="53" idx="2"/>
+          <a:stCxn id="32" idx="2"/>
+          <a:endCxn id="34" idx="0"/>
         </xdr:cNvCxnSpPr>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm flipV="1">
-          <a:off x="5122344" y="1185086"/>
-          <a:ext cx="1" cy="487328"/>
+        <a:xfrm flipH="1">
+          <a:off x="4392051" y="1526691"/>
+          <a:ext cx="1094960" cy="555037"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -2525,28 +2643,28 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>542704</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>144426</xdr:rowOff>
+      <xdr:colOff>377052</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>144912</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>22150</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>89934</xdr:rowOff>
+      <xdr:colOff>381064</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>103012</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="89" name="Straight Arrow Connector 88"/>
+        <xdr:cNvPr id="36" name="Straight Arrow Connector 35"/>
         <xdr:cNvCxnSpPr>
-          <a:stCxn id="40" idx="3"/>
-          <a:endCxn id="48" idx="1"/>
+          <a:stCxn id="8" idx="3"/>
+          <a:endCxn id="32" idx="1"/>
         </xdr:cNvCxnSpPr>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm>
-          <a:off x="3588489" y="2027275"/>
-          <a:ext cx="697760" cy="133793"/>
+        <a:xfrm flipV="1">
+          <a:off x="3425052" y="906912"/>
+          <a:ext cx="1223212" cy="910600"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -2575,24 +2693,24 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>15</xdr:col>
-      <xdr:colOff>55217</xdr:colOff>
-      <xdr:row>28</xdr:row>
-      <xdr:rowOff>179457</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>509093</xdr:colOff>
-      <xdr:row>35</xdr:row>
-      <xdr:rowOff>119103</xdr:rowOff>
+      <xdr:colOff>193261</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>96631</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>39746</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>36277</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="96" name="Rectangle 95"/>
+        <xdr:cNvPr id="37" name="Rectangle 36"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="9166087" y="5590761"/>
+          <a:off x="9304131" y="6280979"/>
           <a:ext cx="1668658" cy="1292472"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2674,533 +2792,854 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>14</xdr:col>
-      <xdr:colOff>1543</xdr:colOff>
-      <xdr:row>28</xdr:row>
-      <xdr:rowOff>118783</xdr:rowOff>
+      <xdr:colOff>42956</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>146391</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
-      <xdr:colOff>55217</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>52649</xdr:rowOff>
+      <xdr:colOff>193261</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>163085</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="38" name="Straight Arrow Connector 37"/>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="26" idx="3"/>
+          <a:endCxn id="37" idx="1"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8546434" y="6910521"/>
+          <a:ext cx="757697" cy="16694"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>141324</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>3120</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>595200</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>105458</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="39" name="Rectangle 38"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6822628" y="3481816"/>
+          <a:ext cx="1668659" cy="875381"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" b="1" u="sng"/>
+            <a:t>EIEOL Glossed Text Gloss</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000"/>
+            <a:t>ID</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000"/>
+            <a:t>Glossed</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" baseline="0"/>
+            <a:t> Text ID</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1000"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000"/>
+            <a:t>Gloss ID</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000"/>
+            <a:t>Order</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1000" baseline="0"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>368262</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>110435</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>391708</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>3120</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="40" name="Straight Arrow Connector 39"/>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="72" idx="2"/>
+          <a:endCxn id="39" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="7656958" y="3202609"/>
+          <a:ext cx="23446" cy="279207"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>442292</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>179457</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>82826</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>36828</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="41" name="Rectangle 40"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4099892" y="3989457"/>
+          <a:ext cx="1469334" cy="619371"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" b="1" u="sng"/>
+            <a:t>EIEOL Language</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000"/>
+            <a:t>ID</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000"/>
+            <a:t>Language</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1000" baseline="0"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>82826</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>108143</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>196471</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>146391</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="42" name="Straight Arrow Connector 41"/>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="41" idx="3"/>
+          <a:endCxn id="26" idx="1"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5549348" y="4359882"/>
+          <a:ext cx="1328427" cy="2550639"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>262282</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>82826</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>108767</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>78242</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="43" name="Rectangle 42"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9406282" y="273326"/>
+          <a:ext cx="1675285" cy="757416"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" b="1" u="sng"/>
+            <a:t>EIEOL Part Of Speech</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000"/>
+            <a:t>ID</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000"/>
+            <a:t>Language</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1000" baseline="0"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>303695</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>96631</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>150180</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>92046</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="44" name="Rectangle 43"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9447695" y="1430131"/>
+          <a:ext cx="1675285" cy="757415"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" b="1" u="sng"/>
+            <a:t>EIEOL Analysis</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000"/>
+            <a:t>ID</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" baseline="0"/>
+            <a:t>Analysis</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>63963</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>80534</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>262282</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>116123</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="45" name="Straight Arrow Connector 44"/>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="43" idx="1"/>
+          <a:endCxn id="30" idx="3"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="8567441" y="660317"/>
+          <a:ext cx="805711" cy="228849"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>63963</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>116123</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>303695</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>94339</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="46" name="Straight Arrow Connector 45"/>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="44" idx="1"/>
+          <a:endCxn id="30" idx="3"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1" flipV="1">
+          <a:off x="8567441" y="889166"/>
+          <a:ext cx="847124" cy="944521"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>124851</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>55216</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>566255</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>179457</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="47" name="Straight Arrow Connector 46"/>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="41" idx="0"/>
+          <a:endCxn id="34" idx="2"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1" flipV="1">
+          <a:off x="4392051" y="3103216"/>
+          <a:ext cx="441404" cy="886241"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>566255</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>193191</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>611</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>179457</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="48" name="Straight Arrow Connector 47"/>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="41" idx="0"/>
+          <a:endCxn id="32" idx="2"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="4833455" y="1526691"/>
+          <a:ext cx="653556" cy="2462766"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>165653</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>151847</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>10372</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>110435</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="72" name="Rectangle 71"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6846957" y="2084456"/>
+          <a:ext cx="1666893" cy="1118153"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" b="1" u="sng"/>
+            <a:t>EIEOL Gloss</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000"/>
+            <a:t>ID</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" b="0" i="0" u="none"/>
+            <a:t>Surface</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" b="0" i="0" u="none" baseline="0"/>
+            <a:t> Form</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1000" b="0" i="0" u="none"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" baseline="0"/>
+            <a:t>Contextual Gloss</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:tabLst/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Language ID</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1000">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1000" baseline="0"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>391708</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>445299</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>151847</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="86" name="Straight Arrow Connector 85"/>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="72" idx="0"/>
+          <a:endCxn id="30" idx="2"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="7680404" y="1546087"/>
+          <a:ext cx="53591" cy="538369"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>483152</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>131142</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>165653</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>69022</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
         <xdr:cNvPr id="94" name="Straight Arrow Connector 93"/>
         <xdr:cNvCxnSpPr>
-          <a:stCxn id="28" idx="3"/>
-          <a:endCxn id="96" idx="1"/>
+          <a:endCxn id="72" idx="1"/>
         </xdr:cNvCxnSpPr>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm>
-          <a:off x="8505021" y="5530087"/>
-          <a:ext cx="661066" cy="706910"/>
-        </a:xfrm>
-        <a:prstGeom prst="straightConnector1">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln>
-          <a:tailEnd type="triangle"/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>141324</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>85946</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>595200</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>188284</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="59" name="Rectangle 58"/>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="6842051" y="2157080"/>
-          <a:ext cx="1672190" cy="855477"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="50000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="en-US" sz="1000" b="1" u="sng"/>
-            <a:t>EIEOL Glossed Text Gloss</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:r>
-            <a:rPr lang="en-US" sz="1000"/>
-            <a:t>ID</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:r>
-            <a:rPr lang="en-US" sz="1000"/>
-            <a:t>Glossed</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1000" baseline="0"/>
-            <a:t> Text ID</a:t>
-          </a:r>
-          <a:endParaRPr lang="en-US" sz="1000"/>
-        </a:p>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:r>
-            <a:rPr lang="en-US" sz="1000"/>
-            <a:t>Gloss ID</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:r>
-            <a:rPr lang="en-US" sz="1000"/>
-            <a:t>Order</a:t>
-          </a:r>
-          <a:endParaRPr lang="en-US" sz="1000" baseline="0"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>368262</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>155058</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>542812</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>85946</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="64" name="Straight Arrow Connector 63"/>
-        <xdr:cNvCxnSpPr>
-          <a:stCxn id="37" idx="2"/>
-          <a:endCxn id="59" idx="0"/>
-        </xdr:cNvCxnSpPr>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm flipH="1">
-          <a:off x="7678146" y="1661337"/>
-          <a:ext cx="174550" cy="495743"/>
-        </a:xfrm>
-        <a:prstGeom prst="straightConnector1">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln>
-          <a:tailEnd type="triangle"/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>69574</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>41412</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>523450</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>36827</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="42" name="Rectangle 41"/>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="9180444" y="4293151"/>
-          <a:ext cx="1668658" cy="768459"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="50000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="en-US" sz="1000" b="1" u="sng"/>
-            <a:t>EIEOL Language</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:r>
-            <a:rPr lang="en-US" sz="1000"/>
-            <a:t>ID</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:r>
-            <a:rPr lang="en-US" sz="1000"/>
-            <a:t>Language</a:t>
-          </a:r>
-          <a:endParaRPr lang="en-US" sz="1000" baseline="0"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>1543</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>82826</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>55217</xdr:colOff>
-      <xdr:row>28</xdr:row>
-      <xdr:rowOff>118783</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="43" name="Straight Arrow Connector 42"/>
-        <xdr:cNvCxnSpPr>
-          <a:endCxn id="28" idx="3"/>
-        </xdr:cNvCxnSpPr>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm flipH="1">
-          <a:off x="8505021" y="4721087"/>
-          <a:ext cx="661066" cy="809000"/>
-        </a:xfrm>
-        <a:prstGeom prst="straightConnector1">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln>
-          <a:tailEnd type="triangle"/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>262282</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>82826</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>108767</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>78242</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="46" name="Rectangle 45"/>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="9373152" y="276087"/>
-          <a:ext cx="1668658" cy="768459"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="50000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="en-US" sz="1000" b="1" u="sng"/>
-            <a:t>EIEOL Part Of Speech</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:r>
-            <a:rPr lang="en-US" sz="1000"/>
-            <a:t>ID</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:r>
-            <a:rPr lang="en-US" sz="1000"/>
-            <a:t>Language</a:t>
-          </a:r>
-          <a:endParaRPr lang="en-US" sz="1000" baseline="0"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>303695</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>96631</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>150180</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>92046</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="49" name="Rectangle 48"/>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="9414565" y="1449457"/>
-          <a:ext cx="1668658" cy="768459"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="50000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="en-US" sz="1000" b="1" u="sng"/>
-            <a:t>EIEOL Analysis</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:r>
-            <a:rPr lang="en-US" sz="1000"/>
-            <a:t>ID</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:r>
-            <a:rPr lang="en-US" sz="1000" baseline="0"/>
-            <a:t>Analysis</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>160593</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>80534</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>262282</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>97022</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="50" name="Straight Arrow Connector 49"/>
-        <xdr:cNvCxnSpPr>
-          <a:stCxn id="46" idx="1"/>
-          <a:endCxn id="37" idx="3"/>
-        </xdr:cNvCxnSpPr>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm flipH="1">
-          <a:off x="8664071" y="660317"/>
-          <a:ext cx="709081" cy="209748"/>
-        </a:xfrm>
-        <a:prstGeom prst="straightConnector1">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln>
-          <a:tailEnd type="triangle"/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>160593</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>97022</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>303695</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>94339</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="56" name="Straight Arrow Connector 55"/>
-        <xdr:cNvCxnSpPr>
-          <a:stCxn id="49" idx="1"/>
-          <a:endCxn id="37" idx="3"/>
-        </xdr:cNvCxnSpPr>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm flipH="1" flipV="1">
-          <a:off x="8664071" y="870065"/>
-          <a:ext cx="750494" cy="963622"/>
+        <a:xfrm flipV="1">
+          <a:off x="4734891" y="2643533"/>
+          <a:ext cx="2112066" cy="1483967"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>

--- a/Documentation/LRC ERD.xlsx
+++ b/Documentation/LRC ERD.xlsx
@@ -2983,15 +2983,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>442292</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>179457</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>82826</xdr:colOff>
+      <xdr:colOff>207618</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>165652</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>455544</xdr:colOff>
       <xdr:row>24</xdr:row>
-      <xdr:rowOff>36828</xdr:rowOff>
+      <xdr:rowOff>124239</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -3000,8 +3000,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4099892" y="3989457"/>
-          <a:ext cx="1469334" cy="619371"/>
+          <a:off x="3851966" y="3644348"/>
+          <a:ext cx="1462708" cy="1118152"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3046,7 +3046,20 @@
             <a:rPr lang="en-US" sz="1000"/>
             <a:t>Language</a:t>
           </a:r>
-          <a:endParaRPr lang="en-US" sz="1000" baseline="0"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" baseline="0"/>
+            <a:t>Custom Keyboard layout</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" baseline="0"/>
+            <a:t>Custom Sort</a:t>
+          </a:r>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -3054,10 +3067,10 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>82826</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>108143</xdr:rowOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>455544</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>144946</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>11</xdr:col>
@@ -3075,8 +3088,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5549348" y="4359882"/>
-          <a:ext cx="1328427" cy="2550639"/>
+          <a:off x="5314674" y="4203424"/>
+          <a:ext cx="1563101" cy="2707097"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -3165,10 +3178,9 @@
         <a:p>
           <a:pPr algn="l"/>
           <a:r>
-            <a:rPr lang="en-US" sz="1000"/>
-            <a:t>Language</a:t>
-          </a:r>
-          <a:endParaRPr lang="en-US" sz="1000" baseline="0"/>
+            <a:rPr lang="en-US" sz="1000" baseline="0"/>
+            <a:t>Part of Speecb</a:t>
+          </a:r>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -3354,9 +3366,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>566255</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>179457</xdr:rowOff>
+      <xdr:colOff>331581</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>165652</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -3368,8 +3380,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipH="1" flipV="1">
-          <a:off x="4392051" y="3103216"/>
-          <a:ext cx="441404" cy="886241"/>
+          <a:off x="4376590" y="3147390"/>
+          <a:ext cx="206730" cy="496958"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -3398,15 +3410,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>566255</xdr:colOff>
+      <xdr:colOff>331581</xdr:colOff>
       <xdr:row>7</xdr:row>
       <xdr:rowOff>193191</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
       <xdr:colOff>611</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>179457</xdr:rowOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>165652</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -3418,8 +3430,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipV="1">
-          <a:off x="4833455" y="1526691"/>
-          <a:ext cx="653556" cy="2462766"/>
+          <a:off x="4583320" y="1546017"/>
+          <a:ext cx="883813" cy="2098331"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -3619,27 +3631,28 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>483152</xdr:colOff>
+      <xdr:colOff>331581</xdr:colOff>
       <xdr:row>13</xdr:row>
       <xdr:rowOff>131142</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>11</xdr:col>
       <xdr:colOff>165653</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>69022</xdr:rowOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>165652</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
         <xdr:cNvPr id="94" name="Straight Arrow Connector 93"/>
         <xdr:cNvCxnSpPr>
+          <a:stCxn id="41" idx="0"/>
           <a:endCxn id="72" idx="1"/>
         </xdr:cNvCxnSpPr>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipV="1">
-          <a:off x="4734891" y="2643533"/>
-          <a:ext cx="2112066" cy="1483967"/>
+          <a:off x="4583320" y="2643533"/>
+          <a:ext cx="2263637" cy="1000815"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>

--- a/Documentation/LRC ERD.xlsx
+++ b/Documentation/LRC ERD.xlsx
@@ -1,13 +1,8 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="153222"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\pype\cola\lrc-site\Documentation\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9303"/>
+  <workbookPr/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="11805" windowHeight="5145"/>
   </bookViews>
@@ -4300,7 +4295,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -4308,11 +4303,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <pageSetup scale="70" orientation="landscape" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/Documentation/LRC ERD.xlsx
+++ b/Documentation/LRC ERD.xlsx
@@ -1053,13 +1053,6 @@
           </a:r>
         </a:p>
         <a:p>
-          <a:pPr algn="l"/>
-          <a:r>
-            <a:rPr lang="en-US" sz="1000" baseline="0"/>
-            <a:t>reflex</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
           <a:r>
             <a:rPr lang="en-US" sz="1100" baseline="0">
               <a:solidFill>
@@ -1475,7 +1468,7 @@
       <xdr:col>6</xdr:col>
       <xdr:colOff>498400</xdr:colOff>
       <xdr:row>25</xdr:row>
-      <xdr:rowOff>121834</xdr:rowOff>
+      <xdr:rowOff>13804</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
@@ -1490,8 +1483,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4142748" y="4953356"/>
-          <a:ext cx="1357000" cy="1300014"/>
+          <a:off x="4142748" y="4845326"/>
+          <a:ext cx="1357000" cy="1408044"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1566,6 +1559,13 @@
             <a:t>Sub Family ID</a:t>
           </a:r>
         </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" baseline="0"/>
+            <a:t>Override Family</a:t>
+          </a:r>
+        </a:p>
       </xdr:txBody>
     </xdr:sp>
     <xdr:clientData/>
@@ -1575,7 +1575,7 @@
       <xdr:col>5</xdr:col>
       <xdr:colOff>487325</xdr:colOff>
       <xdr:row>28</xdr:row>
-      <xdr:rowOff>192059</xdr:rowOff>
+      <xdr:rowOff>138044</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
@@ -1593,8 +1593,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipH="1">
-          <a:off x="3524282" y="5603363"/>
-          <a:ext cx="618466" cy="1069675"/>
+          <a:off x="3524282" y="5549348"/>
+          <a:ext cx="618466" cy="1123690"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -3833,7 +3833,7 @@
           <a:pPr algn="l"/>
           <a:r>
             <a:rPr lang="en-US" sz="1000" baseline="0"/>
-            <a:t>Part of Speech ID</a:t>
+            <a:t>Text</a:t>
           </a:r>
         </a:p>
         <a:p>
@@ -4012,6 +4012,139 @@
         <a:xfrm flipH="1" flipV="1">
           <a:off x="1529554" y="5943746"/>
           <a:ext cx="323853" cy="729292"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>41413</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>151847</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>221280</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>91493</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="58" name="Rectangle 57"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1863587" y="8075543"/>
+          <a:ext cx="1394650" cy="905950"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" b="1" u="sng"/>
+            <a:t>Lex </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" b="1" u="sng" baseline="0"/>
+            <a:t> Reflex_Entry</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1000" baseline="0"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" baseline="0"/>
+            <a:t>ID</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" baseline="0"/>
+            <a:t>Reflex ID</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" baseline="0"/>
+            <a:t>Entry</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>131347</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>259280</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>151847</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="63" name="Straight Arrow Connector 62"/>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="14" idx="2"/>
+          <a:endCxn id="58" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="2560912" y="7343913"/>
+          <a:ext cx="127933" cy="731630"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -4295,7 +4428,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>

--- a/Documentation/LRC ERD.xlsx
+++ b/Documentation/LRC ERD.xlsx
@@ -4040,15 +4040,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>41413</xdr:colOff>
+      <xdr:colOff>151848</xdr:colOff>
       <xdr:row>41</xdr:row>
-      <xdr:rowOff>151847</xdr:rowOff>
+      <xdr:rowOff>165652</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>221280</xdr:colOff>
+      <xdr:colOff>331715</xdr:colOff>
       <xdr:row>46</xdr:row>
-      <xdr:rowOff>91493</xdr:rowOff>
+      <xdr:rowOff>105298</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -4057,7 +4057,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1863587" y="8075543"/>
+          <a:off x="1974022" y="8089348"/>
           <a:ext cx="1394650" cy="905950"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -4123,7 +4123,7 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>131347</xdr:colOff>
+      <xdr:colOff>241782</xdr:colOff>
       <xdr:row>38</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
@@ -4131,7 +4131,7 @@
       <xdr:col>4</xdr:col>
       <xdr:colOff>259280</xdr:colOff>
       <xdr:row>41</xdr:row>
-      <xdr:rowOff>151847</xdr:rowOff>
+      <xdr:rowOff>165652</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -4143,8 +4143,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipH="1">
-          <a:off x="2560912" y="7343913"/>
-          <a:ext cx="127933" cy="731630"/>
+          <a:off x="2671347" y="7343913"/>
+          <a:ext cx="17498" cy="745435"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -4428,7 +4428,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>

--- a/Documentation/LRC ERD.xlsx
+++ b/Documentation/LRC ERD.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9303"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fmcgrath\workspace\lrc-site\Documentation\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="11805" windowHeight="5145"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25200" windowHeight="11985"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
@@ -2566,15 +2571,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>118782</xdr:colOff>
+      <xdr:colOff>229217</xdr:colOff>
       <xdr:row>10</xdr:row>
-      <xdr:rowOff>38684</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>572658</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>110433</xdr:rowOff>
+      <xdr:rowOff>149119</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>75702</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>27607</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2583,7 +2588,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4370521" y="1971293"/>
+          <a:off x="4480956" y="2081728"/>
           <a:ext cx="1668659" cy="1038053"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2651,7 +2656,7 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>345721</xdr:colOff>
+      <xdr:colOff>456156</xdr:colOff>
       <xdr:row>7</xdr:row>
       <xdr:rowOff>151778</xdr:rowOff>
     </xdr:from>
@@ -2659,7 +2664,7 @@
       <xdr:col>10</xdr:col>
       <xdr:colOff>221481</xdr:colOff>
       <xdr:row>10</xdr:row>
-      <xdr:rowOff>38684</xdr:rowOff>
+      <xdr:rowOff>149119</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -2671,8 +2676,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipH="1">
-          <a:off x="5204851" y="1504604"/>
-          <a:ext cx="1090543" cy="466689"/>
+          <a:off x="5315286" y="1504604"/>
+          <a:ext cx="980108" cy="577124"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -2701,28 +2706,28 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>377052</xdr:colOff>
+      <xdr:colOff>340774</xdr:colOff>
       <xdr:row>4</xdr:row>
       <xdr:rowOff>103499</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
       <xdr:colOff>601934</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>103012</xdr:rowOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>30980</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
         <xdr:cNvPr id="36" name="Straight Arrow Connector 35"/>
         <xdr:cNvCxnSpPr>
-          <a:stCxn id="8" idx="3"/>
+          <a:stCxn id="2" idx="3"/>
           <a:endCxn id="32" idx="1"/>
         </xdr:cNvCxnSpPr>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipV="1">
-          <a:off x="3414009" y="876542"/>
-          <a:ext cx="2047055" cy="965818"/>
+          <a:off x="3377731" y="876542"/>
+          <a:ext cx="2083333" cy="2439873"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -3432,9 +3437,9 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>345721</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>110433</xdr:rowOff>
+      <xdr:colOff>456156</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>27607</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
@@ -3452,8 +3457,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipH="1" flipV="1">
-          <a:off x="5204851" y="3009346"/>
-          <a:ext cx="1228251" cy="386523"/>
+          <a:off x="5315286" y="3119781"/>
+          <a:ext cx="1117816" cy="276088"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -4428,7 +4433,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>

--- a/Documentation/LRC ERD.xlsx
+++ b/Documentation/LRC ERD.xlsx
@@ -1,13 +1,8 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9303"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fmcgrath\workspace\lrc-site\Documentation\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="25200" windowHeight="11985"/>
   </bookViews>
@@ -2508,10 +2503,10 @@
           <a:r>
             <a:rPr lang="en-US" sz="1000" baseline="0">
               <a:solidFill>
-                <a:srgbClr val="FF0000"/>
+                <a:schemeClr val="bg1"/>
               </a:solidFill>
             </a:rPr>
-            <a:t>Etyma ID - add later</a:t>
+            <a:t>Etyma ID</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -4433,7 +4428,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>

--- a/Documentation/LRC ERD.xlsx
+++ b/Documentation/LRC ERD.xlsx
@@ -1,15 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9303"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fmcgrath\workspace\lrc-site\Documentation\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="25200" windowHeight="11985"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="152511" concurrentCalc="0"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -4428,7 +4433,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
